--- a/human_validation/judge/kor/judge_D021_S001_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S001_P001__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,313 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 얼마나 적게 먹는지 클리닉에서 걱정을 하셔서요. 대부분 날에는 창고 가기 전에 커피만 마시고, GED 수업 끝나고 나서 요거트나 몇 입 정도 먹어요. 제대로 된 식사를 하면 제가 맞춰놓으려는 모든 게 흐트러지는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 정식으로 한 끼 식사를 하는 걸 생각하면, 체중이 늘까 봐 걱정되시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 휴게실에서 튀긴 음식을 먹거나 교회에서 큰 접시로 먹으면, 바로 몸에 티가 날까 봐 무서워요. 그러면 그 생각이 계속 멈추질 않고 체중계를 확인하고 싶어져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 짧은 시간 동안 통제력을 잃고 평소보다 훨씬 많은 양의 음식을 드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 보통 그런 지경까지는 안 가려고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 현재 키와 체중을 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 지금 정확한 키나 체중은 몰라요. 작업복 바지가 헐렁해지고 있고, 사람들이 계속 저더러 너무 말랐다고 하는 건 아는데, 숫자가 내려가면 드디어 뭔가 이뤄지고 있다는 느낌이 들어요. 왜 그걸 다시 되돌려야 하는지 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 생리를 하신다면, 주기가 규칙적이었나요, 아니면 최근에 멈췄거나 변화가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그걸 꼼꼼하게 챙겨본 적이 없어서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 마지막으로 체중을 재셨을 때 체중계에 대략 얼마나 나왔나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 정확한 숫자는 기억이 안 나요. 그냥 내려갔다는 건 아는데, 드디어 진전을 이루고 있는 느낌이었어요. 바지가 헐렁하고 사람들이 너무 말랐다고 해도, 다시 체중을 늘려야 한다는 생각은 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 체중을 조절하려고 일부러 토하거나 변비약이나 다이어트약 같은 걸 사용하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 다이어트약이 정확히 뭘 말씀하시는 건지 잘 모르겠어요. 그런 걸 하고 있다고 생각해 본 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 클리닉에 방문하셨을 때 체중을 알려주셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 알려주셨을 수도 있는데, 정확한 숫자에는 별로 신경을 안 썼어요. 그냥 낮아졌다는 것만 알았고, 솔직히 드디어 뭔가 이뤄지고 있다는 느낌이었어요. 작업복 바지가 헐렁하고 사람들은 저더러 너무 말랐다고 하는데, 왜 체중을 다시 늘려야 하는지 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 칼로리를 태우거나 체중을 줄이려고 일부러 운동하거나 신체 활동을 유지하려고 애쓰시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 가끔 활동적이긴 한데, 칼로리를 태운다는 관점으로 딱히 생각하진 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 거울로 자신을 볼 때, 과체중이거나 몸의 특정 부위가 너무 크다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네. 수업이나 소프트볼 하기 전에 거울을 보면, 배랑 허벅지가 여전히 있어야 할 크기보다 더 커 보여요. 그게 제가 하루를 어떻게 느끼는지를 좌우하는 것 같아요. 잘하고 있다는 느낌 아니면 실패하고 있다는 느낌이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 체중을 조절하려고 이뇨제를 사용하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 아니요, 이뇨제는 사용한 적 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 이게 시작된 이후로 체중이 대략 얼마나 빠지셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 정확한 양은 모르겠어요. 지금 작업복 바지가 헐렁하고, 사람들이 계속 너무 말랐다고 하는데, 숫자가 내려가면 드디어 뭔가 이뤄지고 있다는 느낌이 들어요. 왜 그걸 다시 되돌려야 하는지 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 체중을 조절하려고 먹은 후에 일부러 토하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 정확히 무슨 뜻인지 잘 모르겠어요. 제가 그러고 있다는 건 딱히 느낀 적 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 클리닉의 의료진이 저체중이라고 말씀하셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 의사 선생님이랑 교회 사람들이 제가 저체중이라 걱정된다고 하셨어요. 그냥 그분들이 실제보다 크게 부풀리는 것 같아요. 저는 여전히 일하고, 수업도 듣고, 제 생활을 잘 유지하고 있거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 식욕부진증 (D021)
 인구통계: 성별 여성 / 나이 26 / 직업상태 packer or packager / 최종학력 고등학교 중퇴
@@ -575,362 +873,37 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S043
-배경 서술: 재리트자가 물류 코디네이터 트랙 자격을 얻고자 하는 마음으로 야간 GED 수업에 등록하면서, 안 그래도 불규칙했던 창고 근무 일정이 근무 교대, 숙제, 소프트볼, 푸드뱅크 봉사활동 사이에서 빡빡하게 채워지게 되었다. 처음에 그녀는 식사를 줄이는 것을 시간을 절약하고 학업을 위해 절제된 생활을 유지하는 실용적인 방법으로 여겼지만, 시간이 지나면서 그 절식은 더 큰 통제감을 느끼고 몸의 변화로 스스로를 평가하는 것을 중심으로 굳어져 갔다. 체중이 건강한 수준보다 훨씬 낮아진 뒤에도, 그녀는 교회와 등산 모임 사람들이 과민 반응을 보이고 있으며 체중이 늘면 지금까지 노력해서 이룬 진전을 잃는 것이라고 주장했다. 창고 건강 검진 양식을 위해 필수로 방문해야 했던 1차 진료에서 그녀의 저체중과 그 심각성에 대한 단호한 부정이 우려를 불러일으켜 의뢰로 이어졌고, 그녀는 그렇게 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 얼마나 적게 먹는지 클리닉에서 걱정을 하셔서요. 대부분 날에는 창고 가기 전에 커피만 마시고, GED 수업 끝나고 나서 요거트나 몇 입 정도 먹어요. 제대로 된 식사를 하면 제가 맞춰놓으려는 모든 게 흐트러지는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 정식으로 한 끼 식사를 하는 걸 생각하면, 체중이 늘까 봐 걱정되시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 휴게실에서 튀긴 음식을 먹거나 교회에서 큰 접시로 먹으면, 바로 몸에 티가 날까 봐 무서워요. 그러면 그 생각이 계속 멈추질 않고 체중계를 확인하고 싶어져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 짧은 시간 동안 통제력을 잃고 평소보다 훨씬 많은 양의 음식을 드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 그런 것 같지 않아요. 보통 그런 지경까지는 안 가려고 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 현재 키와 체중을 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 지금 정확한 키나 체중은 몰라요. 작업복 바지가 헐렁해지고 있고, 사람들이 계속 저더러 너무 말랐다고 하는 건 아는데, 숫자가 내려가면 드디어 뭔가 이뤄지고 있다는 느낌이 들어요. 왜 그걸 다시 되돌려야 하는지 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 생리를 하신다면, 주기가 규칙적이었나요, 아니면 최근에 멈췄거나 변화가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그걸 꼼꼼하게 챙겨본 적이 없어서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 마지막으로 체중을 재셨을 때 체중계에 대략 얼마나 나왔나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 정확한 숫자는 기억이 안 나요. 그냥 내려갔다는 건 아는데, 드디어 진전을 이루고 있는 느낌이었어요. 바지가 헐렁하고 사람들이 너무 말랐다고 해도, 다시 체중을 늘려야 한다는 생각은 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 체중을 조절하려고 일부러 토하거나 변비약이나 다이어트약 같은 걸 사용하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 다이어트약이 정확히 뭘 말씀하시는 건지 잘 모르겠어요. 그런 걸 하고 있다고 생각해 본 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 클리닉에 방문하셨을 때 체중을 알려주셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 알려주셨을 수도 있는데, 정확한 숫자에는 별로 신경을 안 썼어요. 그냥 낮아졌다는 것만 알았고, 솔직히 드디어 뭔가 이뤄지고 있다는 느낌이었어요. 작업복 바지가 헐렁하고 사람들은 저더러 너무 말랐다고 하는데, 왜 체중을 다시 늘려야 하는지 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 칼로리를 태우거나 체중을 줄이려고 일부러 운동하거나 신체 활동을 유지하려고 애쓰시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 가끔 활동적이긴 한데, 칼로리를 태운다는 관점으로 딱히 생각하진 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 거울로 자신을 볼 때, 과체중이거나 몸의 특정 부위가 너무 크다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네. 수업이나 소프트볼 하기 전에 거울을 보면, 배랑 허벅지가 여전히 있어야 할 크기보다 더 커 보여요. 그게 제가 하루를 어떻게 느끼는지를 좌우하는 것 같아요. 잘하고 있다는 느낌 아니면 실패하고 있다는 느낌이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 체중을 조절하려고 이뇨제를 사용하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 아니요, 이뇨제는 사용한 적 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 이게 시작된 이후로 체중이 대략 얼마나 빠지셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 정확한 양은 모르겠어요. 지금 작업복 바지가 헐렁하고, 사람들이 계속 너무 말랐다고 하는데, 숫자가 내려가면 드디어 뭔가 이뤄지고 있다는 느낌이 들어요. 왜 그걸 다시 되돌려야 하는지 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 체중을 조절하려고 먹은 후에 일부러 토하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 정확히 무슨 뜻인지 잘 모르겠어요. 제가 그러고 있다는 건 딱히 느낀 적 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 클리닉의 의료진이 저체중이라고 말씀하셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 의사 선생님이랑 교회 사람들이 제가 저체중이라 걱정된다고 하셨어요. 그냥 그분들이 실제보다 크게 부풀리는 것 같아요. 저는 여전히 일하고, 수업도 듣고, 제 생활을 잘 유지하고 있거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+배경 서술: 재리트자가 물류 코디네이터 트랙 자격을 얻고자 하는 마음으로 야간 GED 수업에 등록하면서, 안 그래도 불규칙했던 창고 근무 일정이 근무 교대, 숙제, 소프트볼, 푸드뱅크 봉사활동 사이에서 빡빡하게 채워지게 되었다. 처음에 그녀는 식사를 줄이는 것을 시간을 절약하고 학업을 위해 절제된 생활을 유지하는 실용적인 방법으로 여겼지만, 시간이 지나면서 그 절식은 더 큰 통제감을 느끼고 몸의 변화로 스스로를 평가하는 것을 중심으로 굳어져 갔다. 체중이 건강한 수준보다 훨씬 낮아진 뒤에도, 그녀는 교회와 등산 모임 사람들이 과민 반응을 보이고 있으며 체중이 늘면 지금까지 노력해서 이룬 진전을 잃는 것이라고 주장했다. 창고 건강 검진 양식을 위해 필수로 방문해야 했던 1차 진료에서 그녀의 저체중과 그 심각성에 대한 단호한 부정이 우려를 불러일으켜 의뢰로 이어졌고, 그녀는 그렇게 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S043 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - S044 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - S045 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - S046 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
+  - S084 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
+        </is>
+      </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 신경성 식욕부진증 (D021) | 배제됨: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.; 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.; 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.; 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.; 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 신경성 식욕부진증 (D021, ICD: F50.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: anorexia_nervosa (관계=must_include, 요구개수=4, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 섭취 제한: 필요량에 비해 에너지 섭취를 지속적으로 제한하여 체중이 현저히 낮아짐.
+  - 저체중: 나이, 성별, 발달 궤적, 신체 건강에 비추어 최소한의 건강 수준보다 현저히 낮은 체중.
+  - 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
+  - 저체중 심각성 미인식: 현재의 저체중 상태가 심각하다는 것을 지속적으로 인식하지 못함.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S001_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S001_P001__gemini-3.8-flash_kor.xlsx
@@ -859,6 +859,11 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -899,11 +904,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D021_S001_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D021_S001_P001__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3269</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
